--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -21737,16 +21737,16 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
         <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -19169,16 +19169,16 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O115" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.1358940373222322</v>
+        <v>0.1432396609612718</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22359,6 +22359,154 @@
       <c r="BC134" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22395,7 +22543,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -22478,7 +22626,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
@@ -22488,7 +22636,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11">
@@ -22540,7 +22688,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.1110149228479591</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1602,9 +1593,6 @@
       <c r="O7" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -1750,9 +1738,6 @@
       <c r="O8" t="n">
         <v>1</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -2146,9 +2131,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -4022,9 +4004,6 @@
       <c r="O22" t="n">
         <v>2</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4415,9 +4394,6 @@
       <c r="O24" t="n">
         <v>8</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.08881193827836725</v>
       </c>
@@ -4563,9 +4539,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -4711,9 +4684,6 @@
       <c r="O26" t="n">
         <v>4</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.007751879695168184</v>
       </c>
@@ -4859,9 +4829,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5255,9 +5222,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -7131,9 +7095,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7524,9 +7485,6 @@
       <c r="O43" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.03330447685438772</v>
       </c>
@@ -7672,9 +7630,6 @@
       <c r="O44" t="n">
         <v>0</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
@@ -7820,9 +7775,6 @@
       <c r="O45" t="n">
         <v>5</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.009689849618960231</v>
       </c>
@@ -7968,9 +7920,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8364,9 +8313,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -10092,9 +10038,6 @@
       <c r="O59" t="n">
         <v>64</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.2350599564492666</v>
       </c>
@@ -10240,9 +10183,6 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10633,9 +10573,6 @@
       <c r="O62" t="n">
         <v>7</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -10781,9 +10718,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10929,9 +10863,6 @@
       <c r="O64" t="n">
         <v>9</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.01744172931412841</v>
       </c>
@@ -11077,9 +11008,6 @@
       <c r="O65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -11473,9 +11401,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13053,9 +12978,6 @@
       <c r="O77" t="n">
         <v>65</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.2387327682687863</v>
       </c>
@@ -13201,9 +13123,6 @@
       <c r="O78" t="n">
         <v>2</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="S78" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13594,9 +13513,6 @@
       <c r="O80" t="n">
         <v>11</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.122116415132755</v>
       </c>
@@ -13742,9 +13658,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13890,9 +13803,6 @@
       <c r="O82" t="n">
         <v>12</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.02325563908550455</v>
       </c>
@@ -14038,9 +13948,6 @@
       <c r="O83" t="n">
         <v>1</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -14434,9 +14341,6 @@
       <c r="O85" t="n">
         <v>1</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -14830,9 +14734,6 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -16458,9 +16359,6 @@
       <c r="O98" t="n">
         <v>44</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.1616037200588708</v>
       </c>
@@ -16606,9 +16504,6 @@
       <c r="O99" t="n">
         <v>14</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.1554208919871427</v>
       </c>
@@ -16754,9 +16649,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -16902,9 +16794,6 @@
       <c r="O101" t="n">
         <v>22</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.04263533832342501</v>
       </c>
@@ -17050,9 +16939,6 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0</v>
       </c>
@@ -17446,9 +17332,6 @@
       <c r="O104" t="n">
         <v>1</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -17842,9 +17725,6 @@
       <c r="O106" t="n">
         <v>1</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -17990,9 +17870,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -18138,9 +18015,6 @@
       <c r="O108" t="n">
         <v>3</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.0008595114398308156</v>
       </c>
@@ -18286,9 +18160,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -18434,9 +18305,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -18582,9 +18450,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -18730,9 +18595,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -18878,9 +18740,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -19026,9 +18885,6 @@
       <c r="O114" t="n">
         <v>1</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -19174,9 +19030,6 @@
       <c r="O115" t="n">
         <v>39</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.1432396609612718</v>
       </c>
@@ -19322,9 +19175,6 @@
       <c r="O116" t="n">
         <v>10</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01937969923792046</v>
       </c>
@@ -19470,9 +19320,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19866,9 +19713,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -20262,9 +20106,6 @@
       <c r="O121" t="n">
         <v>0</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0</v>
       </c>
@@ -20410,9 +20251,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -20558,9 +20396,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -20706,9 +20541,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -20854,9 +20686,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -21002,9 +20831,6 @@
       <c r="O126" t="n">
         <v>2</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -21150,9 +20976,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -21298,9 +21121,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -21446,9 +21266,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -21594,9 +21411,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -21737,16 +21551,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -21890,9 +21701,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -22286,9 +22094,6 @@
       <c r="O134" t="n">
         <v>1</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -22432,9 +22237,6 @@
         <v>0</v>
       </c>
       <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
         <v>0</v>
       </c>
       <c r="R135" t="n">
@@ -22688,7 +22490,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -19170,13 +19170,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R116" t="n">
-        <v>0.01937969923792046</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -19025,13 +19025,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="O115" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R115" t="n">
-        <v>0.1432396609612718</v>
+        <v>0.157930908239351</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -7090,10 +7090,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -7246,10 +7246,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -10178,10 +10178,10 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -10334,10 +10334,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -16460,12 +16460,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -16499,81 +16499,92 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O99" t="n">
-        <v>14</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.1554208919871427</v>
+        <v>1</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16600,17 +16611,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -16644,81 +16655,170 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
-      </c>
-      <c r="R100" t="n">
-        <v>0</v>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Q Fever</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary q fever notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16750,12 +16850,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -16789,13 +16889,13 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O101" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R101" t="n">
-        <v>0.04263533832342501</v>
+        <v>0.1554208919871427</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -16828,42 +16928,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -16895,12 +16995,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -16947,82 +17047,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA102" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO102" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ102" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS102" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -17049,17 +17135,17 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -17093,170 +17179,81 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O103" t="n">
-        <v>0</v>
-      </c>
-      <c r="U103" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V103" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W103" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X103" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y103" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA103" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD103" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE103" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF103" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG103" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH103" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN103" t="b">
-        <v>1</v>
+        <v>22</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.04263533832342501</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ103" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS103" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17288,12 +17285,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -17327,13 +17324,13 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
@@ -17342,7 +17339,7 @@
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -17367,7 +17364,7 @@
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -17380,42 +17377,42 @@
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17447,12 +17444,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -17486,24 +17483,24 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
@@ -17533,7 +17530,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -17568,17 +17565,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -17601,7 +17598,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -17614,42 +17611,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -17681,12 +17678,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -17726,75 +17723,89 @@
         <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17821,17 +17832,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -17856,7 +17867,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
@@ -17865,81 +17876,170 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" t="n">
-        <v>0</v>
-      </c>
-      <c r="R107" t="n">
-        <v>0</v>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -17971,12 +18071,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18001,7 +18101,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -18010,13 +18110,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O108" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R108" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -18049,42 +18149,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18146,7 +18246,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -18291,7 +18391,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -18300,13 +18400,13 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S110" t="inlineStr">
         <is>
@@ -18436,7 +18536,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -18581,7 +18681,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -18590,13 +18690,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -18726,7 +18826,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -18871,7 +18971,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -18880,13 +18980,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -18986,12 +19086,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -19016,22 +19116,22 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.157930908239351</v>
+        <v>0</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -19064,42 +19164,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19131,12 +19231,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -19161,22 +19261,22 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N116" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O116" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="R116" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -19209,42 +19309,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19276,12 +19376,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19315,95 +19415,81 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="O117" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>0.1689493436979103</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ117" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS117" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -19430,17 +19516,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19474,170 +19560,81 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O118" t="n">
-        <v>0</v>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.01744172931412841</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19669,12 +19666,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -19708,13 +19705,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -19723,7 +19720,7 @@
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -19748,7 +19745,7 @@
       </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
@@ -19761,42 +19758,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -19828,12 +19825,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -19867,24 +19864,24 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X120" t="inlineStr">
@@ -19914,7 +19911,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr">
@@ -19949,17 +19946,17 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN120" t="b">
@@ -19982,7 +19979,7 @@
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -19995,42 +19992,42 @@
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20062,12 +20059,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20092,7 +20089,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -20101,81 +20098,95 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20202,17 +20213,17 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20237,7 +20248,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -20246,81 +20257,170 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
-      </c>
-      <c r="R122" t="n">
-        <v>0</v>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20382,7 +20482,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -20527,7 +20627,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -20536,13 +20636,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -20672,7 +20772,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -20817,7 +20917,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -20826,13 +20926,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R126" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -20962,7 +21062,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21107,7 +21207,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21116,13 +21216,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21252,7 +21352,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -21367,12 +21467,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21397,12 +21497,12 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N130" t="n">
@@ -21445,42 +21545,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21512,12 +21612,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21542,22 +21642,22 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>0.003875939847584092</v>
+        <v>0</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -21590,42 +21690,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21657,12 +21757,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21709,82 +21809,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA132" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ132" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS132" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR132" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21811,17 +21897,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21855,170 +21941,81 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V133" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X133" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y133" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA133" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD133" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG133" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM133" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN133" t="b">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.003875939847584092</v>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO133" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ133" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS133" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR133" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22050,12 +22047,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22089,81 +22086,95 @@
         </is>
       </c>
       <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP134" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT134" t="n">
         <v>1</v>
       </c>
-      <c r="O134" t="n">
-        <v>1</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP134" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
-      <c r="AT134" t="n">
-        <v>0</v>
-      </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22190,123 +22201,502 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ135" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT135" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA135" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB135" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC135" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N136" t="n">
+        <v>1</v>
+      </c>
+      <c r="O136" t="n">
+        <v>1</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA136" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB136" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC136" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
         <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>D113</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>Q fever</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
         <is>
           <t>Q热</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
+      <c r="L137" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr">
+      <c r="M137" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N135" t="n">
-        <v>0</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
+      <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0</v>
+      </c>
+      <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO135" t="inlineStr">
+      <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP135" t="inlineStr">
+      <c r="AP137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR135" t="inlineStr">
+      <c r="AR137" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS135" t="inlineStr"/>
-      <c r="AT135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV135" t="inlineStr">
+      <c r="AV137" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW135" t="inlineStr">
+      <c r="AW137" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX135" t="inlineStr">
+      <c r="AX137" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY135" t="inlineStr">
+      <c r="AY137" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ135" t="inlineStr">
+      <c r="AZ137" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA135" t="inlineStr">
+      <c r="BA137" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB135" t="inlineStr">
+      <c r="BB137" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC135" t="inlineStr">
+      <c r="BC137" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -22428,7 +22818,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10">
@@ -22438,7 +22828,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
@@ -22458,7 +22848,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
@@ -22490,7 +22880,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>563</v>
+        <v>569</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -21796,13 +21796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.01836405909759895</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22697,6 +22697,151 @@
         </is>
       </c>
       <c r="BC137" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr"/>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -22735,7 +22880,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -22818,7 +22963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -22828,7 +22973,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -22880,7 +23025,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>569</v>
+        <v>574</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -19415,13 +19415,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="O117" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1689493436979103</v>
+        <v>0.1873134027955093</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -21796,13 +21796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O132" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R132" t="n">
-        <v>0.01836405909759895</v>
+        <v>0.04040093001471769</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22844,6 +22844,151 @@
       <c r="BC138" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>1</v>
+      </c>
+      <c r="O139" t="n">
+        <v>1</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22880,7 +23025,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -22963,7 +23108,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -22973,7 +23118,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -23025,7 +23170,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>574</v>
+        <v>586</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -21796,13 +21796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O132" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R132" t="n">
-        <v>0.04040093001471769</v>
+        <v>0.04774655365375727</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>586</v>
+        <v>588</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -21796,13 +21796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O132" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R132" t="n">
-        <v>0.04774655365375727</v>
+        <v>0.05141936547327706</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -21796,13 +21796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O132" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R132" t="n">
-        <v>0.05141936547327706</v>
+        <v>0.05876498911231665</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -16354,13 +16354,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O98" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R98" t="n">
-        <v>0.1616037200588708</v>
+        <v>0.1689493436979103</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -19415,13 +19415,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="O117" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1873134027955093</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -19560,13 +19560,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O118" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R118" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -21796,13 +21796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="O132" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R132" t="n">
-        <v>0.05876498911231665</v>
+        <v>0.07345623639039579</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21941,13 +21941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O133" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R133" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22989,6 +22989,151 @@
       <c r="BC139" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23025,7 +23170,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -23108,7 +23253,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -23118,7 +23263,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -23170,7 +23315,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>591</v>
+        <v>602</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -19415,13 +19415,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="O117" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.1909862146150291</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -21796,13 +21796,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O132" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R132" t="n">
-        <v>0.07345623639039579</v>
+        <v>0.07712904820991559</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21941,13 +21941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O133" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R133" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -19415,13 +19415,13 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O117" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1909862146150291</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -19521,12 +19521,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19560,13 +19560,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>0.01937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -19599,42 +19599,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19666,12 +19666,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -19705,95 +19705,81 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O119" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>0.01937969923792046</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -19820,7 +19806,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -19869,98 +19855,23 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
+      <c r="R120" t="n">
+        <v>0</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>1</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -20054,17 +19965,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20098,29 +20009,104 @@
         </is>
       </c>
       <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
         <v>1</v>
       </c>
-      <c r="O121" t="n">
-        <v>1</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20138,7 +20124,7 @@
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+          <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -20151,42 +20137,42 @@
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -20213,7 +20199,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -20262,98 +20248,23 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
+      <c r="R122" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="W122" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X122" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y122" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD122" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE122" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF122" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG122" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM122" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN122" t="b">
-        <v>1</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -20447,17 +20358,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20482,7 +20393,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
@@ -20491,81 +20402,170 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
-      </c>
-      <c r="R123" t="n">
-        <v>0</v>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD123" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE123" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG123" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH123" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM123" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN123" t="b">
+        <v>1</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ123" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -20597,12 +20597,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20675,42 +20675,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20742,12 +20742,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -20772,7 +20772,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -20820,42 +20820,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20887,12 +20887,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -20926,13 +20926,13 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
@@ -20965,42 +20965,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21032,12 +21032,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21071,13 +21071,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -21110,42 +21110,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21177,12 +21177,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21216,13 +21216,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -21255,42 +21255,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21322,12 +21322,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -21361,13 +21361,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -21400,42 +21400,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21467,12 +21467,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21545,42 +21545,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21612,12 +21612,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21642,7 +21642,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -21690,42 +21690,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -21757,12 +21757,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21787,22 +21787,22 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N132" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>0.07712904820991559</v>
+        <v>0</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -21835,42 +21835,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21902,12 +21902,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -21941,13 +21941,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="O133" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R133" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.09182029548799475</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -21980,42 +21980,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -22047,12 +22047,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22086,95 +22086,81 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O134" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22201,7 +22187,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -22250,98 +22236,23 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -22435,17 +22346,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22479,81 +22390,170 @@
         </is>
       </c>
       <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD136" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE136" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG136" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH136" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM136" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN136" t="b">
         <v>1</v>
       </c>
-      <c r="O136" t="n">
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ136" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT136" t="n">
         <v>1</v>
       </c>
-      <c r="R136" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr"/>
-      <c r="AT136" t="n">
-        <v>0</v>
-      </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22585,12 +22585,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -22624,13 +22624,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -22663,42 +22663,42 @@
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -22760,7 +22760,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -22875,12 +22875,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -22905,7 +22905,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -22914,13 +22914,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -22953,42 +22953,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23020,12 +23020,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -23059,13 +23059,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23098,40 +23098,185 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW140" t="inlineStr">
+      <c r="AW141" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX140" t="inlineStr">
+      <c r="AX141" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY140" t="inlineStr">
+      <c r="AY141" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ140" t="inlineStr">
+      <c r="AZ141" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA140" t="inlineStr">
+      <c r="BA141" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB140" t="inlineStr">
+      <c r="BB141" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC140" t="inlineStr">
+      <c r="BC141" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -23253,7 +23398,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="10">
@@ -23263,7 +23408,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -23315,7 +23460,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>603</v>
+        <v>608</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1771,17 +1771,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -1997,7 +2002,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2005,17 +2010,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
@@ -2156,7 +2166,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2164,17 +2174,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2390,7 +2405,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2398,17 +2413,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -4854,7 +4874,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -4862,17 +4882,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5088,7 +5113,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5096,17 +5121,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5247,7 +5277,7 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
@@ -5255,17 +5285,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS29" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
@@ -5481,7 +5516,7 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
@@ -5489,17 +5524,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS30" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
@@ -7945,7 +7985,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -7953,17 +7993,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8179,7 +8224,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8187,17 +8232,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -8338,7 +8388,7 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
@@ -8346,17 +8396,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS48" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
@@ -8572,7 +8627,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -8580,17 +8635,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -11033,7 +11093,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -11041,17 +11101,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -11267,7 +11332,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -11275,17 +11340,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -11426,7 +11496,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -11434,17 +11504,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -11660,7 +11735,7 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ68" t="inlineStr">
@@ -11668,17 +11743,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS68" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
@@ -13973,7 +14053,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -13981,17 +14061,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -14207,7 +14292,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -14215,17 +14300,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -14366,7 +14456,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -14374,17 +14464,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -14600,7 +14695,7 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
@@ -14608,17 +14703,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS86" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
@@ -17354,7 +17454,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -17362,17 +17462,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -17588,7 +17693,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -17596,17 +17701,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -17747,7 +17857,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -17755,17 +17865,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -17981,7 +18096,7 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
@@ -17989,17 +18104,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS107" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
@@ -19880,7 +20000,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -19888,17 +20008,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -20114,7 +20239,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -20122,17 +20247,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -20273,7 +20403,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -20281,17 +20411,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS122" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -20507,7 +20642,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -20515,17 +20650,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS123" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -21941,13 +22081,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O133" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R133" t="n">
-        <v>0.09182029548799475</v>
+        <v>0.09549310730751455</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22261,7 +22401,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -22269,17 +22409,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS135" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
@@ -22495,7 +22640,7 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
@@ -22503,17 +22648,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS136" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
@@ -23460,7 +23610,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -4409,13 +4409,13 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R24" t="n">
-        <v>0.08881193827836725</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -16560,12 +16560,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -16599,67 +16599,53 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
           <t>missing_population</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -16669,17 +16655,17 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
@@ -16711,17 +16697,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -16755,145 +16741,53 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
-        <v>1</v>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V100" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X100" t="inlineStr">
-        <is>
-          <t>Q Fever</t>
-        </is>
-      </c>
-      <c r="Y100" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA100" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD100" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG100" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH100" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary q fever notifications; confirmed cases only under the July 2026 technical notes.</t>
-        </is>
-      </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN100" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP100" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ100" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV100" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -16903,17 +16797,17 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
@@ -16950,12 +16844,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -16989,17 +16883,14 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="O101" t="n">
-        <v>14</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.1554208919871427</v>
+        <v>24</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -17028,42 +16919,42 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17095,12 +16986,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -17139,12 +17030,9 @@
       <c r="O102" t="n">
         <v>0</v>
       </c>
-      <c r="R102" t="n">
-        <v>0</v>
-      </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -17173,42 +17061,42 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17240,12 +17128,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -17279,17 +17167,14 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>22</v>
-      </c>
-      <c r="R103" t="n">
-        <v>0.04263533832342501</v>
+        <v>0</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -17318,42 +17203,42 @@
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17385,12 +17270,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -17424,22 +17309,19 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" t="n">
-        <v>0</v>
-      </c>
-      <c r="R104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -17454,7 +17336,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -17462,62 +17344,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17549,12 +17426,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -17588,29 +17465,29 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
         </is>
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>Q-feber</t>
+          <t>Q Fever</t>
         </is>
       </c>
       <c r="Y105" t="inlineStr">
@@ -17620,7 +17497,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -17635,7 +17512,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD105" t="inlineStr">
@@ -17670,17 +17547,17 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>PHO IDTO current-year monthly preliminary q fever notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -17693,7 +17570,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -17701,62 +17578,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
+          <t>SER_CA_ON_PHO_IDTO_Q_FEVER_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17788,12 +17660,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -17827,100 +17699,81 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R106" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.1554208919871427</v>
       </c>
       <c r="S106" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="AA106" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO106" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ106" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR106" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS106" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -17947,17 +17800,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -17991,175 +17844,81 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA107" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG107" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN107" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ107" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS107" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -18191,12 +17950,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -18230,13 +17989,13 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="R108" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.04263533832342501</v>
       </c>
       <c r="S108" t="inlineStr">
         <is>
@@ -18269,42 +18028,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -18336,12 +18095,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -18366,7 +18125,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -18388,68 +18147,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18476,17 +18254,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -18511,7 +18289,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -18520,81 +18298,175 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
-        <v>3</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18626,12 +18498,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -18656,7 +18528,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -18665,81 +18537,100 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ111" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS111" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18766,17 +18657,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -18801,7 +18692,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -18815,76 +18706,170 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="R112" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE112" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG112" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH112" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM112" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN112" t="b">
+        <v>1</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ112" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS112" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -18916,12 +18901,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -18946,7 +18931,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -18955,13 +18940,13 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -18994,42 +18979,42 @@
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -19061,12 +19046,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -19091,7 +19076,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -19139,42 +19124,42 @@
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19206,12 +19191,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -19236,7 +19221,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -19245,13 +19230,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O115" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -19284,42 +19269,42 @@
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19351,12 +19336,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -19381,7 +19366,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -19390,13 +19375,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -19429,42 +19414,42 @@
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19496,12 +19481,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -19526,22 +19511,22 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>53</v>
+        <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -19574,42 +19559,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19641,12 +19626,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -19671,12 +19656,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N118" t="n">
@@ -19719,42 +19704,42 @@
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19786,12 +19771,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -19816,22 +19801,22 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N119" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>0.01937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -19864,42 +19849,42 @@
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -19931,12 +19916,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -19961,12 +19946,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N120" t="n">
@@ -19983,87 +19968,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA120" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ120" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS120" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20090,17 +20056,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20125,184 +20091,90 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
         <v>1</v>
       </c>
+      <c r="R121" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR121" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20334,12 +20206,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -20373,100 +20245,81 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="O122" t="n">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="R122" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.1946590264345489</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="AA122" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ122" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR122" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS122" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20493,17 +20346,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -20537,175 +20390,78 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
-        <v>1</v>
-      </c>
-      <c r="U123" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA123" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP123" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ123" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS123" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
-        </is>
-      </c>
-      <c r="AT123" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV123" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20737,12 +20493,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -20767,7 +20523,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -20776,17 +20532,14 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -20815,42 +20568,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20882,12 +20635,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -20912,7 +20665,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -20926,12 +20679,9 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="R125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -20960,42 +20710,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21027,12 +20777,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21057,7 +20807,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21066,17 +20816,14 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
-      </c>
-      <c r="R126" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -21105,42 +20852,42 @@
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21172,12 +20919,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -21202,7 +20949,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -21211,17 +20958,14 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -21250,42 +20994,42 @@
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21317,12 +21061,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -21347,7 +21091,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -21361,12 +21105,9 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -21395,42 +21136,42 @@
       </c>
       <c r="AV128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA128" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB128" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC128" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21462,12 +21203,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -21492,7 +21233,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -21501,17 +21242,14 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O129" t="n">
-        <v>2</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0.0005730076265538771</v>
+        <v>5</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -21540,42 +21278,42 @@
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21607,12 +21345,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -21637,7 +21375,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -21651,12 +21389,9 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -21685,42 +21420,42 @@
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21752,12 +21487,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -21782,7 +21517,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -21791,13 +21526,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>0.1110149228479591</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -21830,42 +21565,42 @@
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -21897,12 +21632,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -21927,7 +21662,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -21975,42 +21710,42 @@
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -22042,12 +21777,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -22072,22 +21807,22 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="O133" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="R133" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22120,42 +21855,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -22187,12 +21922,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -22217,90 +21952,109 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0.009689849618960231</v>
+        <v>0</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ134" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT134" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22327,7 +22081,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -22362,12 +22116,12 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N135" t="n">
@@ -22376,23 +22130,98 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U135" t="inlineStr">
         <is>
           <t>SER_NO_FHI_511_MONTHLY</t>
         </is>
       </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD135" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG135" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH135" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM135" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN135" t="b">
+        <v>1</v>
       </c>
       <c r="AO135" t="inlineStr">
         <is>
@@ -22491,17 +22320,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -22526,48 +22355,31 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Q-feber</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -22575,64 +22387,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -22655,7 +22409,7 @@
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_511_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -22668,42 +22422,42 @@
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22730,17 +22484,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -22765,12 +22519,12 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N137" t="n">
@@ -22779,76 +22533,170 @@
       <c r="O137" t="n">
         <v>1</v>
       </c>
-      <c r="R137" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_Q_FEVER</t>
+        </is>
+      </c>
       <c r="AT137" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22910,12 +22758,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N138" t="n">
@@ -23025,12 +22873,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23055,12 +22903,12 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N139" t="n">
@@ -23103,42 +22951,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23170,12 +23018,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23200,22 +23048,22 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -23248,42 +23096,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23315,12 +23163,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23345,22 +23193,22 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
@@ -23393,42 +23241,4020 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW141" t="inlineStr">
+      <c r="AW142" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
+      <c r="AX142" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr">
+      <c r="AY142" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ141" t="inlineStr">
+      <c r="AZ142" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA141" t="inlineStr">
+      <c r="BA142" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB141" t="inlineStr">
+      <c r="BB142" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC141" t="inlineStr">
+      <c r="BC142" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>2</v>
+      </c>
+      <c r="O143" t="n">
+        <v>2</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" t="n">
+        <v>0</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="O146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>39</v>
+      </c>
+      <c r="O147" t="n">
+        <v>39</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0.1432396609612718</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>12</v>
+      </c>
+      <c r="O149" t="n">
+        <v>12</v>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr"/>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>14</v>
+      </c>
+      <c r="O150" t="n">
+        <v>14</v>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="O151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" t="n">
+        <v>0</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>8</v>
+      </c>
+      <c r="O154" t="n">
+        <v>8</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0.01550375939033637</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA155" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB155" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC155" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="O156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT156" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>1</v>
+      </c>
+      <c r="O157" t="n">
+        <v>1</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="O159" t="n">
+        <v>0</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>1</v>
+      </c>
+      <c r="O160" t="n">
+        <v>1</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="O161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA161" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB161" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC161" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
+        <v>1</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" t="n">
+        <v>0</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="O166" t="n">
+        <v>0</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT166" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>q-fever</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="O167" t="n">
+        <v>0</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Q-feber</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_511_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT167" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA167" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB167" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC167" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -23465,7 +27291,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -23548,7 +27374,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
@@ -23558,7 +27384,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -23578,7 +27404,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -23610,7 +27436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>609</v>
+        <v>762</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d113/2026-2029.xlsx
+++ b/diseases/d113/2026-2029.xlsx
@@ -25069,13 +25069,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O154" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R154" t="n">
-        <v>0.01550375939033637</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -27436,7 +27436,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="16">
